--- a/artfynd/A 9508-2025 artfynd.xlsx
+++ b/artfynd/A 9508-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128734548</v>
       </c>
       <c r="B2" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9508-2025 artfynd.xlsx
+++ b/artfynd/A 9508-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128734548</v>
       </c>
       <c r="B2" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9508-2025 artfynd.xlsx
+++ b/artfynd/A 9508-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128734548</v>
       </c>
       <c r="B2" t="n">
-        <v>97493</v>
+        <v>97499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9508-2025 artfynd.xlsx
+++ b/artfynd/A 9508-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128734548</v>
       </c>
       <c r="B2" t="n">
-        <v>97499</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9508-2025 artfynd.xlsx
+++ b/artfynd/A 9508-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128734548</v>
       </c>
       <c r="B2" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9508-2025 artfynd.xlsx
+++ b/artfynd/A 9508-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128734548</v>
       </c>
       <c r="B2" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9508-2025 artfynd.xlsx
+++ b/artfynd/A 9508-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128734548</v>
       </c>
       <c r="B2" t="n">
-        <v>97525</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9508-2025 artfynd.xlsx
+++ b/artfynd/A 9508-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128734548</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9508-2025 artfynd.xlsx
+++ b/artfynd/A 9508-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128734548</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9508-2025 artfynd.xlsx
+++ b/artfynd/A 9508-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128734548</v>
       </c>
       <c r="B2" t="n">
-        <v>97543</v>
+        <v>97552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
